--- a/samples/checked/monthly/月次クレーム集計2605.xlsx
+++ b/samples/checked/monthly/月次クレーム集計2605.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次集計" sheetId="1" r:id="Rf11ecbe362384573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期待結果" sheetId="2" r:id="R48c05876217c4609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="3" r:id="Rf75ed04bd4574ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="異常系" sheetId="4" r:id="R27d9ae4466034576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次集計" sheetId="1" r:id="R31605e4cdae9455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期待結果" sheetId="2" r:id="R52e49f038c3e49bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="3" r:id="R39d8476c4c8948c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="異常系" sheetId="4" r:id="Re53190159a1640fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -288,11 +288,11 @@
   <x:cols>
     <x:col min="1" max="1" width="16.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="1.5" hidden="0" customWidth="1"/>
@@ -325,7 +325,7 @@
     <x:col min="37" max="37" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="38" max="38" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="39" max="39" width="5.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="24.75" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="27.1299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -502,19 +502,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H4" s="5" t="str"/>
       <x:c r="I4" s="5" t="str"/>
@@ -561,19 +561,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str"/>
       <x:c r="I5" s="5" t="str"/>
@@ -620,19 +620,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str"/>
       <x:c r="I6" s="5" t="str"/>
@@ -679,19 +679,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str"/>
       <x:c r="I7" s="5" t="str"/>
@@ -738,11 +738,11 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
-        <x:v>Aster Central subtotal</x:v>
+        <x:v>あかね中央支店 小計</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str"/>
       <x:c r="G8" s="12" t="str"/>
@@ -875,7 +875,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN8" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -883,22 +883,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str"/>
       <x:c r="I9" s="5" t="str"/>
@@ -942,22 +942,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H10" s="5" t="str"/>
       <x:c r="I10" s="5" t="str"/>
@@ -1001,22 +1001,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H11" s="5" t="str"/>
       <x:c r="I11" s="5" t="str"/>
@@ -1060,14 +1060,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str">
-        <x:v>North small-branch subtotal</x:v>
+        <x:v>北部小支店 小計</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str"/>
       <x:c r="G12" s="12" t="str"/>
@@ -1200,7 +1200,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN12" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1208,22 +1208,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H13" s="5" t="str"/>
       <x:c r="I13" s="5" t="str"/>
@@ -1267,22 +1267,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str"/>
       <x:c r="I14" s="5" t="str"/>
@@ -1326,22 +1326,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str"/>
       <x:c r="I15" s="5" t="str"/>
@@ -1385,14 +1385,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str">
-        <x:v>East small-branch subtotal</x:v>
+        <x:v>東部小支店 小計</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str"/>
       <x:c r="G16" s="12" t="str"/>
@@ -1525,7 +1525,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1536,19 +1536,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H17" s="5" t="str"/>
       <x:c r="I17" s="5" t="str"/>
@@ -1595,19 +1595,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H18" s="5" t="str"/>
       <x:c r="I18" s="5" t="str"/>
@@ -1654,19 +1654,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H19" s="5" t="str"/>
       <x:c r="I19" s="5" t="str"/>
@@ -1713,19 +1713,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H20" s="5" t="str"/>
       <x:c r="I20" s="5" t="str"/>
@@ -1772,19 +1772,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str"/>
       <x:c r="I21" s="5" t="str"/>
@@ -1831,11 +1831,11 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str"/>
       <x:c r="E22" s="12" t="str">
-        <x:v>Dahlia Hub subtotal</x:v>
+        <x:v>だりあ東支店 小計</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str"/>
       <x:c r="G22" s="12" t="str"/>
@@ -1968,7 +1968,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1976,22 +1976,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H23" s="5" t="str"/>
       <x:c r="I23" s="5" t="str"/>
@@ -2035,22 +2035,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H24" s="5" t="str"/>
       <x:c r="I24" s="5" t="str"/>
@@ -2094,22 +2094,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H25" s="5" t="str"/>
       <x:c r="I25" s="5" t="str"/>
@@ -2153,22 +2153,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H26" s="5" t="str"/>
       <x:c r="I26" s="5" t="str"/>
@@ -2212,14 +2212,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str"/>
       <x:c r="E27" s="12" t="str">
-        <x:v>South small-branch subtotal</x:v>
+        <x:v>南部小支店 小計</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str"/>
       <x:c r="G27" s="12" t="str"/>
@@ -2352,7 +2352,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2360,22 +2360,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H28" s="5" t="str"/>
       <x:c r="I28" s="5" t="str"/>
@@ -2419,22 +2419,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H29" s="5" t="str"/>
       <x:c r="I29" s="5" t="str"/>
@@ -2478,22 +2478,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H30" s="5" t="str"/>
       <x:c r="I30" s="5" t="str"/>
@@ -2543,11 +2543,11 @@
   <x:cols>
     <x:col min="1" max="1" width="16.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="1.5" hidden="0" customWidth="1"/>
@@ -2580,7 +2580,7 @@
     <x:col min="37" max="37" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="38" max="38" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="39" max="39" width="5.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="24.75" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="27.1299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2757,19 +2757,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H4" s="5" t="n">
         <x:v>1</x:v>
@@ -2817,19 +2817,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str"/>
       <x:c r="I5" s="5" t="str"/>
@@ -2873,19 +2873,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H6" s="5" t="n">
         <x:v>4</x:v>
@@ -2933,19 +2933,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str"/>
       <x:c r="I7" s="5" t="str"/>
@@ -2993,11 +2993,11 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
-        <x:v>Aster Central subtotal</x:v>
+        <x:v>あかね中央支店 小計</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str"/>
       <x:c r="G8" s="12" t="str"/>
@@ -3040,7 +3040,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AN8" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3048,22 +3048,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str"/>
       <x:c r="I9" s="5" t="str"/>
@@ -3104,22 +3104,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H10" s="5" t="str"/>
       <x:c r="I10" s="5" t="str"/>
@@ -3160,22 +3160,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H11" s="5" t="n">
         <x:v>2</x:v>
@@ -3220,14 +3220,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str">
-        <x:v>North small-branch subtotal</x:v>
+        <x:v>北部小支店 小計</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str"/>
       <x:c r="G12" s="12" t="str"/>
@@ -3268,7 +3268,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN12" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3276,22 +3276,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H13" s="5" t="str"/>
       <x:c r="I13" s="5" t="str"/>
@@ -3332,22 +3332,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str"/>
       <x:c r="I14" s="5" t="str"/>
@@ -3392,22 +3392,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str"/>
       <x:c r="I15" s="5" t="str"/>
@@ -3448,14 +3448,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str">
-        <x:v>East small-branch subtotal</x:v>
+        <x:v>東部小支店 小計</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str"/>
       <x:c r="G16" s="12" t="str"/>
@@ -3496,7 +3496,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3507,19 +3507,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H17" s="5" t="str"/>
       <x:c r="I17" s="5" t="str"/>
@@ -3563,19 +3563,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H18" s="5" t="str"/>
       <x:c r="I18" s="5" t="str"/>
@@ -3623,19 +3623,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H19" s="5" t="str"/>
       <x:c r="I19" s="5" t="str"/>
@@ -3683,19 +3683,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H20" s="5" t="str"/>
       <x:c r="I20" s="5" t="str"/>
@@ -3743,19 +3743,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str"/>
       <x:c r="I21" s="5" t="str"/>
@@ -3799,11 +3799,11 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str"/>
       <x:c r="E22" s="12" t="str">
-        <x:v>Dahlia Hub subtotal</x:v>
+        <x:v>だりあ東支店 小計</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str"/>
       <x:c r="G22" s="12" t="str"/>
@@ -3846,7 +3846,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3854,22 +3854,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H23" s="5" t="str"/>
       <x:c r="I23" s="5" t="str"/>
@@ -3914,22 +3914,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H24" s="5" t="str"/>
       <x:c r="I24" s="5" t="str"/>
@@ -3970,22 +3970,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H25" s="5" t="n">
         <x:v>3</x:v>
@@ -4030,22 +4030,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H26" s="5" t="str"/>
       <x:c r="I26" s="5" t="str"/>
@@ -4086,14 +4086,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str"/>
       <x:c r="E27" s="12" t="str">
-        <x:v>South small-branch subtotal</x:v>
+        <x:v>南部小支店 小計</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str"/>
       <x:c r="G27" s="12" t="str"/>
@@ -4138,7 +4138,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4146,22 +4146,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H28" s="5" t="str"/>
       <x:c r="I28" s="5" t="str"/>
@@ -4202,22 +4202,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H29" s="5" t="str"/>
       <x:c r="I29" s="5" t="str"/>
@@ -4262,22 +4262,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H30" s="5" t="str"/>
       <x:c r="I30" s="5" t="str"/>
@@ -4326,33 +4326,33 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.380000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Branch master</x:v>
+        <x:v>支店マスタ</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
-        <x:v>branch_code</x:v>
+        <x:v>支店コード</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>branch_name</x:v>
+        <x:v>支店名</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>region</x:v>
+        <x:v>地域</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>branch_size</x:v>
+        <x:v>支店区分</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>subtotal_group</x:v>
+        <x:v>小計グループ</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4360,13 +4360,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>large</x:v>
+        <x:v>大支店</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4377,16 +4377,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4394,16 +4394,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4411,13 +4411,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>large</x:v>
+        <x:v>大支店</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4428,16 +4428,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4445,29 +4445,29 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>Business line master</x:v>
+        <x:v>業務マスタ</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>business_code</x:v>
+        <x:v>業務コード</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>business_name</x:v>
+        <x:v>業務名</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4475,7 +4475,7 @@
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4483,7 +4483,7 @@
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4491,7 +4491,7 @@
         <x:v>REP</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4499,7 +4499,7 @@
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4507,7 +4507,7 @@
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4515,7 +4515,7 @@
         <x:v>APP</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4523,7 +4523,7 @@
         <x:v>CON</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4531,29 +4531,29 @@
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>Supported branch/business combinations</x:v>
+        <x:v>支店・業務対応表</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
-        <x:v>branch_code</x:v>
+        <x:v>支店コード</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>branch_name</x:v>
+        <x:v>支店名</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>business_code</x:v>
+        <x:v>業務コード</x:v>
       </x:c>
       <x:c r="D24" s="10" t="str">
-        <x:v>business_name</x:v>
+        <x:v>業務名</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
-        <x:v>subtotal_group</x:v>
+        <x:v>小計グループ</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4561,13 +4561,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4578,13 +4578,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4595,13 +4595,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4612,13 +4612,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4629,16 +4629,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4646,16 +4646,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4663,16 +4663,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4680,16 +4680,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E32" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4697,16 +4697,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4714,16 +4714,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="E34" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4731,13 +4731,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4748,13 +4748,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E36" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4765,13 +4765,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4782,13 +4782,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E38" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4799,13 +4799,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B39" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="D39" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="E39" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4816,16 +4816,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B40" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C40" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D40" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E40" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4833,16 +4833,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B41" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="D41" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="E41" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4850,16 +4850,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B42" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C42" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="D42" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="E42" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4867,16 +4867,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B43" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="D43" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="E43" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4884,16 +4884,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B44" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C44" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D44" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E44" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4901,16 +4901,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B45" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C45" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D45" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E45" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4918,16 +4918,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B46" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C46" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="D46" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="E46" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4942,33 +4942,33 @@
     <x:col min="1" max="1" width="6.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="6.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23.8799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>month</x:v>
+        <x:v>対象月</x:v>
       </x:c>
       <x:c r="B1" s="10" t="str">
-        <x:v>date</x:v>
+        <x:v>日付</x:v>
       </x:c>
       <x:c r="C1" s="10" t="str">
-        <x:v>file_name</x:v>
+        <x:v>ファイル名</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>subfolder</x:v>
+        <x:v>サブフォルダ</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>row_no</x:v>
+        <x:v>行番号</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>issue_type</x:v>
+        <x:v>異常種別</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>expected_behavior</x:v>
+        <x:v>期待動作</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -4987,7 +4987,7 @@
         <x:v>missing_day</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
-        <x:v>no transfer; day column remains blank</x:v>
+        <x:v>転記なし。日付列は空欄のまま</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
